--- a/excels/Global.xlsx
+++ b/excels/Global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13420"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="全局配置表|Global" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Tag</t>
   </si>
@@ -78,6 +78,33 @@
   </si>
   <si>
     <t>初始道具</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>DefaultChatRoomHistoryMax</t>
+  </si>
+  <si>
+    <t>聊天室最大历史记录</t>
+  </si>
+  <si>
+    <t>ChatRoomTypeHistoryMax</t>
+  </si>
+  <si>
+    <t>map[chatRoomType]int32</t>
+  </si>
+  <si>
+    <t>{Group: 50}</t>
+  </si>
+  <si>
+    <t>聊天室类型对应的最大历史记录</t>
+  </si>
+  <si>
+    <t>ChatRoomMemberMax</t>
+  </si>
+  <si>
+    <t>聊天室最大成员数量</t>
   </si>
 </sst>
 </file>
@@ -1247,11 +1274,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="12.5384615384615" customWidth="1"/>
+    <col min="2" max="2" width="30.7692307692308" customWidth="1"/>
+    <col min="3" max="3" width="26.4615384615385" customWidth="1"/>
     <col min="4" max="4" width="37.0769230769231" customWidth="1"/>
+    <col min="6" max="6" width="34.5384615384615" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1323,6 +1352,57 @@
       </c>
       <c r="F4" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
